--- a/data/trans_bre/LAWTONB_2R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,0</t>
+          <t>1,02; 10,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 10,64</t>
+          <t>-0,92; 10,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,37</t>
+          <t>2,28; 13,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 17,23</t>
+          <t>6,29; 16,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 86,11</t>
+          <t>7,0; 95,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 52,83</t>
+          <t>-3,98; 51,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 77,0</t>
+          <t>9,81; 79,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,25; 77,72</t>
+          <t>20,9; 73,27</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 12,78</t>
+          <t>-8,7; 12,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 7,27</t>
+          <t>-12,67; 6,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 15,38</t>
+          <t>1,31; 14,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 4,55</t>
+          <t>-10,49; 4,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 191,14</t>
+          <t>-61,27; 195,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 91,87</t>
+          <t>-70,16; 66,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 317,61</t>
+          <t>11,76; 298,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,24; 47,6</t>
+          <t>-77,07; 49,72</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 23,83</t>
+          <t>-8,23; 21,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 29,47</t>
+          <t>-8,92; 31,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 16,79</t>
+          <t>-12,3; 18,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 10,25</t>
+          <t>-2,3; 10,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 542,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 332,4</t>
+          <t>-32,09; 341,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,62</t>
+          <t>1,36; 9,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 10,14</t>
+          <t>0,26; 10,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,75</t>
+          <t>4,31; 12,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 13,12</t>
+          <t>-5,13; 12,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 91,11</t>
+          <t>9,57; 89,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 56,63</t>
+          <t>1,28; 57,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,49; 96,5</t>
+          <t>24,97; 101,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 82,61</t>
+          <t>-27,7; 80,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/LAWTONB_2R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>12,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,33</t>
+          <t>0,81; 10,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 10,34</t>
+          <t>-1,45; 10,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,43</t>
+          <t>1,72; 13,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 16,98</t>
+          <t>7,15; 17,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 95,09</t>
+          <t>3,94; 85,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 51,28</t>
+          <t>-5,32; 48,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 79,17</t>
+          <t>6,32; 76,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,9; 73,27</t>
+          <t>23,68; 77,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-27,42%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 12,61</t>
+          <t>-9,84; 12,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 6,5</t>
+          <t>-13,36; 6,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,76</t>
+          <t>1,3; 15,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 4,9</t>
+          <t>-0,04; 8,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,27; 195,92</t>
+          <t>-67,32; 193,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 66,01</t>
+          <t>-72,37; 72,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 298,89</t>
+          <t>6,35; 294,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,07; 49,72</t>
+          <t>-1,29; 100,69</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 21,55</t>
+          <t>-7,33; 23,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 31,36</t>
+          <t>-11,2; 27,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 18,17</t>
+          <t>-13,85; 15,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 10,34</t>
+          <t>-2,77; 10,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 542,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 341,0</t>
+          <t>-34,89; 291,42</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>12,42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,7</t>
+          <t>1,27; 9,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 10,19</t>
+          <t>-0,05; 9,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,81</t>
+          <t>4,25; 12,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 12,71</t>
+          <t>9,11; 15,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 89,44</t>
+          <t>6,46; 91,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 57,77</t>
+          <t>-0,9; 54,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,97; 101,9</t>
+          <t>23,95; 98,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 80,2</t>
+          <t>50,92; 107,78</t>
         </is>
       </c>
     </row>
